--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -285,7 +285,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
-    <t>Messbefunde.Hueftumfang</t>
+    <t>Messbefunde.hueftumfang</t>
   </si>
   <si>
     <t>Event</t>
@@ -972,7 +972,7 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
-    <t>Messbefunde.Hueftumfang.Datum</t>
+    <t>Messbefunde.hueftumfang.Datum</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="521">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -285,7 +285,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
-    <t>Messbefunde.hueftumfang</t>
+    <t>koerperlicheUntersuchung.hueftumfang</t>
   </si>
   <si>
     <t>Event</t>
@@ -889,7 +889,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>Patient</t>
+    <t>persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -972,7 +972,7 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
-    <t>Messbefunde.hueftumfang.Datum</t>
+    <t>koerperlicheUntersuchung.hueftumfang.datumHueftumfang</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1089,6 +1089,9 @@
   </si>
   <si>
     <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>koerperlicheUntersuchung.hueftumfang.hueftumfang</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -6456,7 +6459,7 @@
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>88</v>
+        <v>343</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
@@ -6465,7 +6468,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6476,10 +6479,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6505,20 +6508,20 @@
         <v>113</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="R38" t="s" s="2">
         <v>82</v>
@@ -6542,10 +6545,10 @@
         <v>177</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6563,7 +6566,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6587,7 +6590,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6598,10 +6601,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6627,21 +6630,21 @@
         <v>195</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>82</v>
@@ -6683,7 +6686,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6707,7 +6710,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6718,10 +6721,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6747,21 +6750,21 @@
         <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>82</v>
@@ -6803,7 +6806,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6812,7 +6815,7 @@
         <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>105</v>
@@ -6827,7 +6830,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6838,10 +6841,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6867,23 +6870,23 @@
         <v>113</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>82</v>
@@ -6925,7 +6928,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6949,7 +6952,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6960,10 +6963,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6989,16 +6992,16 @@
         <v>186</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7023,13 +7026,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7047,7 +7050,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7056,7 +7059,7 @@
         <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>105</v>
@@ -7071,7 +7074,7 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7082,14 +7085,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7111,16 +7114,16 @@
         <v>186</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7145,13 +7148,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7169,7 +7172,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7190,24 +7193,24 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7230,19 +7233,19 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7291,7 +7294,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7315,7 +7318,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7326,10 +7329,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7355,13 +7358,13 @@
         <v>186</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7390,10 +7393,10 @@
         <v>265</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7411,7 +7414,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7432,24 +7435,24 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7475,16 +7478,16 @@
         <v>186</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7512,10 +7515,10 @@
         <v>265</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7533,7 +7536,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7557,7 +7560,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7568,10 +7571,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7594,16 +7597,16 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7653,7 +7656,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7674,24 +7677,24 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7714,16 +7717,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7773,7 +7776,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7794,24 +7797,24 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7834,19 +7837,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7895,7 +7898,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7907,7 +7910,7 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7919,7 +7922,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7930,10 +7933,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8048,10 +8051,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8168,14 +8171,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8197,10 +8200,10 @@
         <v>137</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>140</v>
@@ -8255,7 +8258,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8290,10 +8293,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8316,13 +8319,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8373,7 +8376,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8382,7 +8385,7 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8397,7 +8400,7 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8408,10 +8411,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8434,13 +8437,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8491,7 +8494,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8500,7 +8503,7 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>105</v>
@@ -8515,7 +8518,7 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8526,10 +8529,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8555,16 +8558,16 @@
         <v>186</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8592,10 +8595,10 @@
         <v>117</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8613,7 +8616,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8634,10 +8637,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8648,10 +8651,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8677,16 +8680,16 @@
         <v>186</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8714,10 +8717,10 @@
         <v>265</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8735,7 +8738,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8756,10 +8759,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8770,10 +8773,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8796,17 +8799,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8855,7 +8858,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8890,10 +8893,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8919,10 +8922,10 @@
         <v>195</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8973,7 +8976,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8997,7 +9000,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9008,10 +9011,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9034,16 +9037,16 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9093,7 +9096,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9117,7 +9120,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9128,10 +9131,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9154,16 +9157,16 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9213,7 +9216,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9237,7 +9240,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9248,10 +9251,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9274,19 +9277,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9335,7 +9338,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9359,7 +9362,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9370,10 +9373,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9488,10 +9491,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9608,14 +9611,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9637,10 +9640,10 @@
         <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>140</v>
@@ -9695,7 +9698,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9730,10 +9733,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9759,13 +9762,13 @@
         <v>186</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>263</v>
@@ -9817,7 +9820,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>93</v>
@@ -9838,7 +9841,7 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>270</v>
@@ -9852,10 +9855,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9878,16 +9881,16 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>327</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>329</v>
@@ -9939,7 +9942,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9960,7 +9963,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>332</v>
@@ -9974,10 +9977,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10003,16 +10006,16 @@
         <v>186</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10037,13 +10040,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10061,7 +10064,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10070,7 +10073,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10085,7 +10088,7 @@
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10096,14 +10099,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10125,16 +10128,16 @@
         <v>186</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10159,13 +10162,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10183,7 +10186,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10204,24 +10207,24 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10247,16 +10250,16 @@
         <v>83</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10305,7 +10308,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10329,7 +10332,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -825,7 +825,7 @@
 </t>
   </si>
   <si>
-    <t>Hüftumfang an der maximalen Gesäßprotuberanz</t>
+    <t>Hüftumfang</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -839,9 +839,9 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="56063-1"/&gt;
-    &lt;display value="Circumference.at maximal protrusion of gluteus muscles Pelvis"/&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="284472007"/&gt;
+    &lt;display value="Hip circumference"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hueftumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
